--- a/data/mock/상품 목데이터/golajulgaenyang_full_schema_mockdata_product_thumbnails_linked.xlsx
+++ b/data/mock/상품 목데이터/golajulgaenyang_full_schema_mockdata_product_thumbnails_linked.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enums" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="brands" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_groups" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="products" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_images" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_target_species" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_allergens" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_cautions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_ingredients" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventories" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stock_events" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review_pet" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review_health_concern" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review_image" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review_question" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review_recommend" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users_mock" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="breed_reference" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="validation" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_thumbnail_mapping" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="product_thumbnail_preview" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="enums" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="brands" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="product_groups" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="products" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="product_images" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="product_target_species" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="product_allergens" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="product_cautions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="product_ingredients" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="inventories" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="stock_events" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="review" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="review_pet" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="review_health_concern" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="review_image" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="review_question" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="review_recommend" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="users_mock" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="breed_reference" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="validation" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="product_thumbnail_mapping" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="product_thumbnail_preview" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -273,7 +273,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -288,13 +288,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -313,13 +316,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -338,13 +344,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -363,13 +372,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -388,13 +400,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -413,13 +428,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -438,13 +456,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -463,13 +484,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -488,13 +512,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -513,13 +540,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -538,13 +568,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -563,13 +596,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -588,13 +624,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -613,13 +652,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -638,13 +680,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -663,13 +708,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -688,13 +736,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -713,13 +764,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -738,13 +792,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -763,13 +820,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -788,13 +848,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -813,13 +876,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -838,13 +904,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -863,13 +932,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -888,13 +960,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -913,13 +988,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -938,13 +1016,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -963,13 +1044,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -988,13 +1072,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1013,13 +1100,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1038,13 +1128,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1063,13 +1156,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1088,13 +1184,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1113,13 +1212,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1138,13 +1240,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1163,13 +1268,16 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1658,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="18" min="1" max="1"/>
@@ -1808,6 +1916,18 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>Helper 시트(users_mock, breed_reference)는 캡처된 DB 테이블이 아니라 화면 검증/매핑을 위한 보조 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>별점 분포</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>현실적인 J자형 분포로 조정 (5점 180 / 4점 55 / 3점 18 / 2점 10 / 1점 24). 1~2점 리뷰는 review_question.review_answer 에 NEGATIVE 값 사용 (기존 POSITIVE/NEUTRAL 에 추가)</t>
         </is>
       </c>
     </row>
@@ -5714,11 +5834,11 @@
         <v>1</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>보리 반응은 좋은 편이에요. 사료 냄새가 너무 강하지 않아요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>보리 반응은 보통이에요. 다만 사료를 거의 먹지 않고 남겼어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L9" s="22" t="n">
@@ -5754,11 +5874,11 @@
         <v>1</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>하루가 처음부터 잘 먹었어요. 급여 후 배변도 크게 문제 없었어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>하루에게는 아쉬운 제품이었어요. 사료를 거의 먹지 않고 남겼어요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L10" s="22" t="n">
@@ -6394,11 +6514,11 @@
         <v>3</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K26" s="22" t="inlineStr">
         <is>
-          <t>별이가 처음부터 잘 먹었어요. 급여 후 배변도 크게 문제 없었어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>별이에게는 맞지 않았어요. 기존에 없던 가려움이 생겼어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L26" s="22" t="n">
@@ -6514,11 +6634,11 @@
         <v>3</v>
       </c>
       <c r="J29" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="22" t="inlineStr">
         <is>
-          <t>두부 반응은 좋은 편이에요. 알갱이 크기가 무난해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>두부 반응은 보통이에요. 다만 사료를 거의 먹지 않고 남겼어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L29" s="22" t="n">
@@ -6754,11 +6874,11 @@
         <v>4</v>
       </c>
       <c r="J35" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" s="22" t="inlineStr">
         <is>
-          <t>몽이 반응은 좋은 편이에요. 알갱이 크기가 무난해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>몽이에게는 그냥 무난한 정도였어요. 다만 냄새를 맡고 고개를 돌려요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L35" s="22" t="n">
@@ -6914,11 +7034,11 @@
         <v>5</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K39" s="22" t="inlineStr">
         <is>
-          <t>콩이가 처음부터 잘 먹었어요. 사료 토핑으로도 잘 먹어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>콩이 반응이 기대보다 별로였어요. 기대한 만큼 잘 먹지 않아요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L39" s="22" t="n">
@@ -7194,11 +7314,11 @@
         <v>6</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K46" s="22" t="inlineStr">
         <is>
-          <t>하루가 처음부터 잘 먹었어요. 사료 토핑으로도 잘 먹어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>하루에게는 맞지 않았어요. 한두 번 먹고 더는 안 먹으려 해요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L46" s="22" t="n">
@@ -7234,11 +7354,11 @@
         <v>6</v>
       </c>
       <c r="J47" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K47" s="22" t="inlineStr">
         <is>
-          <t>탄이 반응은 좋은 편이에요. 부스러기가 많지 않아 편해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>탄이 반응은 보통이에요. 다만 소분이 어렵고 흘리기 쉬워요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L47" s="22" t="n">
@@ -7274,11 +7394,11 @@
         <v>6</v>
       </c>
       <c r="J48" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48" s="22" t="inlineStr">
         <is>
-          <t>몽이 반응은 좋은 편이에요. 간식 반응이 좋아요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>몽이에게는 그냥 무난한 정도였어요. 다만 한두 번 먹고 더는 안 먹으려 해요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L48" s="22" t="n">
@@ -7434,11 +7554,11 @@
         <v>7</v>
       </c>
       <c r="J52" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K52" s="22" t="inlineStr">
         <is>
-          <t>몽이가 처음부터 잘 먹었어요. 간식 반응이 좋아요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>몽이에게는 맞지 않았어요. 피부가 붉어지고 털이 푸석해졌어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L52" s="22" t="n">
@@ -7514,11 +7634,11 @@
         <v>7</v>
       </c>
       <c r="J54" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K54" s="22" t="inlineStr">
         <is>
-          <t>코코가 처음부터 잘 먹었어요. 사료 토핑으로도 잘 먹어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>코코이 먹고 나서 문제가 있었어요. 기대한 만큼 잘 먹지 않아요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L54" s="22" t="n">
@@ -7554,11 +7674,11 @@
         <v>7</v>
       </c>
       <c r="J55" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K55" s="22" t="inlineStr">
         <is>
-          <t>구름가 처음부터 잘 먹었어요. 사료 토핑으로도 잘 먹어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>구름에게는 맞지 않았어요. 급여 후 묽은 변을 봤어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L55" s="22" t="n">
@@ -7754,11 +7874,11 @@
         <v>7</v>
       </c>
       <c r="J60" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K60" s="22" t="inlineStr">
         <is>
-          <t>탄이 반응은 좋은 편이에요. 한입 크기로 주기 편해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>탄이에게는 그냥 무난한 정도였어요. 다만 간식인데도 관심을 보이지 않아요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L60" s="22" t="n">
@@ -7794,11 +7914,11 @@
         <v>7</v>
       </c>
       <c r="J61" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K61" s="22" t="inlineStr">
         <is>
-          <t>호두 반응은 좋은 편이에요. 간식 반응이 좋아요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>호두 반응은 보통이에요. 다만 한두 번 먹고 더는 안 먹으려 해요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L61" s="22" t="n">
@@ -7874,11 +7994,11 @@
         <v>8</v>
       </c>
       <c r="J63" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K63" s="22" t="inlineStr">
         <is>
-          <t>호두가 처음부터 잘 먹었어요. 부스러기가 많지 않아 편해요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>호두이 먹고 나서 문제가 있었어요. 기대한 만큼 잘 먹지 않아요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L63" s="22" t="n">
@@ -8194,11 +8314,11 @@
         <v>9</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K71" s="22" t="inlineStr">
         <is>
-          <t>루이 반응은 좋은 편이에요. 사료에 섞거나 같이 주기 쉬워요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>루이 반응은 보통이에요. 다만 급여 자체가 힘들어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L71" s="22" t="n">
@@ -8274,11 +8394,11 @@
         <v>9</v>
       </c>
       <c r="J73" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K73" s="22" t="inlineStr">
         <is>
-          <t>봉구가 처음부터 잘 먹었어요. 개별 급여량 관리가 편해요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>봉구이 먹고 나서 문제가 있었어요. 구토 증상이 있어서 급여를 멈췄어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L73" s="22" t="n">
@@ -8874,11 +8994,11 @@
         <v>12</v>
       </c>
       <c r="J88" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K88" s="22" t="inlineStr">
         <is>
-          <t>모찌 반응은 좋은 편이에요. 사료에 섞거나 같이 주기 쉬워요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>모찌 반응은 보통이에요. 다만 영양제를 먹이려고 하면 피해요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L88" s="22" t="n">
@@ -9034,11 +9154,11 @@
         <v>13</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K92" s="22" t="inlineStr">
         <is>
-          <t>두부가 처음부터 잘 먹었어요. 기호성이 괜찮은 편이에요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>두부 반응이 기대보다 별로였어요. 냄새를 맡고 고개를 돌려요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L92" s="22" t="n">
@@ -9114,11 +9234,11 @@
         <v>13</v>
       </c>
       <c r="J94" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K94" s="22" t="inlineStr">
         <is>
-          <t>별이가 처음부터 잘 먹었어요. 알갱이 크기가 무난해요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>별이에게는 맞지 않았어요. 급여 후 묽은 변을 봤어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L94" s="22" t="n">
@@ -9394,11 +9514,11 @@
         <v>13</v>
       </c>
       <c r="J101" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K101" s="22" t="inlineStr">
         <is>
-          <t>루이가 처음부터 잘 먹었어요. 기호성이 괜찮은 편이에요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>루이이 먹고 나서 문제가 있었어요. 사료를 거의 먹지 않고 남겼어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L101" s="22" t="n">
@@ -9594,11 +9714,11 @@
         <v>14</v>
       </c>
       <c r="J106" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K106" s="22" t="inlineStr">
         <is>
-          <t>호두가 처음부터 잘 먹었어요. 사료 냄새가 너무 강하지 않아요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>호두 반응이 기대보다 별로였어요. 사료를 거의 먹지 않고 남겼어요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L106" s="22" t="n">
@@ -9794,11 +9914,11 @@
         <v>14</v>
       </c>
       <c r="J111" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K111" s="22" t="inlineStr">
         <is>
-          <t>하루가 처음부터 잘 먹었어요. 사료 냄새가 너무 강하지 않아요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>하루이 먹고 나서 문제가 있었어요. 기존 사료보다 먹는 양이 확 줄었어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L111" s="22" t="n">
@@ -9834,11 +9954,11 @@
         <v>14</v>
       </c>
       <c r="J112" s="22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K112" s="22" t="inlineStr">
         <is>
-          <t>보리 반응은 좋은 편이에요. 알갱이 크기가 무난해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>보리에게는 아쉬운 제품이었어요. 피부가 붉어지고 털이 푸석해졌어요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L112" s="22" t="n">
@@ -9914,11 +10034,11 @@
         <v>14</v>
       </c>
       <c r="J114" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K114" s="22" t="inlineStr">
         <is>
-          <t>구름 반응은 좋은 편이에요. 알갱이 크기가 무난해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>구름 반응은 보통이에요. 다만 기존 사료보다 먹는 양이 확 줄었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L114" s="22" t="n">
@@ -9954,11 +10074,11 @@
         <v>15</v>
       </c>
       <c r="J115" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K115" s="22" t="inlineStr">
         <is>
-          <t>콩이가 처음부터 잘 먹었어요. 기호성이 괜찮은 편이에요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>콩이에게 권하고 싶지 않아요. 피부가 붉어지고 털이 푸석해졌어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L115" s="22" t="n">
@@ -10154,11 +10274,11 @@
         <v>15</v>
       </c>
       <c r="J120" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K120" s="22" t="inlineStr">
         <is>
-          <t>구름 반응은 좋은 편이에요. 알갱이 크기가 무난해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>구름 반응은 보통이에요. 다만 사료를 거의 먹지 않고 남겼어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L120" s="22" t="n">
@@ -10354,11 +10474,11 @@
         <v>16</v>
       </c>
       <c r="J125" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K125" s="22" t="inlineStr">
         <is>
-          <t>호두가 처음부터 잘 먹었어요. 기호성이 괜찮은 편이에요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>호두에게 권하고 싶지 않아요. 냄새를 맡고 고개를 돌려요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L125" s="22" t="n">
@@ -10794,11 +10914,11 @@
         <v>17</v>
       </c>
       <c r="J136" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K136" s="22" t="inlineStr">
         <is>
-          <t>하루가 처음부터 잘 먹었어요. 부스러기가 많지 않아 편해요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>하루 반응이 기대보다 별로였어요. 기존에 없던 가려움이 생겼어요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L136" s="22" t="n">
@@ -10834,11 +10954,11 @@
         <v>17</v>
       </c>
       <c r="J137" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K137" s="22" t="inlineStr">
         <is>
-          <t>탄이 반응은 좋은 편이에요. 사료 토핑으로도 잘 먹어요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>탄이 반응은 보통이에요. 다만 먹고 나서 배변 상태가 안 좋아졌어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L137" s="22" t="n">
@@ -10954,11 +11074,11 @@
         <v>17</v>
       </c>
       <c r="J140" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K140" s="22" t="inlineStr">
         <is>
-          <t>탄이가 처음부터 잘 먹었어요. 간식 반응이 좋아요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>탄이에게는 아쉬운 제품이었어요. 간식인데도 관심을 보이지 않아요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L140" s="22" t="n">
@@ -11034,11 +11154,11 @@
         <v>17</v>
       </c>
       <c r="J142" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K142" s="22" t="inlineStr">
         <is>
-          <t>몽이가 처음부터 잘 먹었어요. 사료 토핑으로도 잘 먹어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>몽이이 먹고 나서 문제가 있었어요. 간식인데도 관심을 보이지 않아요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L142" s="22" t="n">
@@ -11354,11 +11474,11 @@
         <v>18</v>
       </c>
       <c r="J150" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K150" s="22" t="inlineStr">
         <is>
-          <t>두부가 처음부터 잘 먹었어요. 사료 토핑으로도 잘 먹어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>두부이 먹고 나서 문제가 있었어요. 포장이 불편해서 급여하기 어려워요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L150" s="22" t="n">
@@ -11434,11 +11554,11 @@
         <v>18</v>
       </c>
       <c r="J152" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K152" s="22" t="inlineStr">
         <is>
-          <t>콩이가 처음부터 잘 먹었어요. 부스러기가 많지 않아 편해요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>콩이에게는 맞지 않았어요. 기대한 만큼 잘 먹지 않아요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L152" s="22" t="n">
@@ -11474,11 +11594,11 @@
         <v>19</v>
       </c>
       <c r="J153" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K153" s="22" t="inlineStr">
         <is>
-          <t>두부 반응은 좋은 편이에요. 한입 크기로 주기 편해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>두부 반응은 보통이에요. 다만 포장이 불편해서 급여하기 어려워요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L153" s="22" t="n">
@@ -11954,11 +12074,11 @@
         <v>20</v>
       </c>
       <c r="J165" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K165" s="22" t="inlineStr">
         <is>
-          <t>루이 반응은 좋은 편이에요. 부스러기가 많지 않아 편해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>루이 반응은 보통이에요. 다만 알레르기 반응이 의심돼서 중단했어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L165" s="22" t="n">
@@ -12394,11 +12514,11 @@
         <v>21</v>
       </c>
       <c r="J176" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K176" s="22" t="inlineStr">
         <is>
-          <t>보리 반응은 좋은 편이에요. 매일 급여하기 편해요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>보리에게는 그냥 무난한 정도였어요. 다만 섞어줘도 알아채고 안 먹어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L176" s="22" t="n">
@@ -12434,11 +12554,11 @@
         <v>21</v>
       </c>
       <c r="J177" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K177" s="22" t="inlineStr">
         <is>
-          <t>몽이가 처음부터 잘 먹었어요. 꾸준히 먹이기 부담 없어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>몽이에게는 아쉬운 제품이었어요. 급여 자체가 힘들어요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L177" s="22" t="n">
@@ -12514,11 +12634,11 @@
         <v>22</v>
       </c>
       <c r="J179" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K179" s="22" t="inlineStr">
         <is>
-          <t>코코가 처음부터 잘 먹었어요. 개별 급여량 관리가 편해요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>코코에게는 아쉬운 제품이었어요. 섞어줘도 알아채고 안 먹어요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L179" s="22" t="n">
@@ -13394,11 +13514,11 @@
         <v>25</v>
       </c>
       <c r="J201" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K201" s="22" t="inlineStr">
         <is>
-          <t>루나가 처음부터 잘 먹었어요. 급여 후 배변도 크게 문제 없었어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>루나에게는 맞지 않았어요. 사료를 거의 먹지 않고 남겼어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L201" s="22" t="n">
@@ -13434,11 +13554,11 @@
         <v>25</v>
       </c>
       <c r="J202" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K202" s="22" t="inlineStr">
         <is>
-          <t>두부 반응은 좋은 편이에요. 급여 후 배변도 크게 문제 없었어요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>두부에게는 그냥 무난한 정도였어요. 다만 냄새를 맡고 고개를 돌려요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L202" s="22" t="n">
@@ -13594,11 +13714,11 @@
         <v>25</v>
       </c>
       <c r="J206" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K206" s="22" t="inlineStr">
         <is>
-          <t>마루 반응은 좋은 편이에요. 사료 냄새가 너무 강하지 않아요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>마루 반응은 보통이에요. 다만 기존 사료보다 먹는 양이 확 줄었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L206" s="22" t="n">
@@ -14194,11 +14314,11 @@
         <v>27</v>
       </c>
       <c r="J221" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K221" s="22" t="inlineStr">
         <is>
-          <t>탄이가 처음부터 잘 먹었어요. 기호성이 괜찮은 편이에요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>탄이에게는 맞지 않았어요. 냄새를 맡고 고개를 돌려요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L221" s="22" t="n">
@@ -14314,11 +14434,11 @@
         <v>27</v>
       </c>
       <c r="J224" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K224" s="22" t="inlineStr">
         <is>
-          <t>루나가 처음부터 잘 먹었어요. 알갱이 크기가 무난해요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>루나에게 권하고 싶지 않아요. 급여 후 긁는 횟수가 늘었어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L224" s="22" t="n">
@@ -15034,11 +15154,11 @@
         <v>30</v>
       </c>
       <c r="J242" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K242" s="22" t="inlineStr">
         <is>
-          <t>쿠키가 처음부터 잘 먹었어요. 부스러기가 많지 않아 편해요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>쿠키에게 권하고 싶지 않아요. 한두 번 먹고 더는 안 먹으려 해요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L242" s="22" t="n">
@@ -15194,11 +15314,11 @@
         <v>30</v>
       </c>
       <c r="J246" s="22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K246" s="22" t="inlineStr">
         <is>
-          <t>쿠키가 처음부터 잘 먹었어요. 사료 토핑으로도 잘 먹어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>쿠키에게는 아쉬운 제품이었어요. 기대한 만큼 잘 먹지 않아요. 재구매는 고민 중이에요.</t>
         </is>
       </c>
       <c r="L246" s="22" t="n">
@@ -15434,11 +15554,11 @@
         <v>31</v>
       </c>
       <c r="J252" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K252" s="22" t="inlineStr">
         <is>
-          <t>하루가 처음부터 잘 먹었어요. 간식 반응이 좋아요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>하루이 먹고 나서 문제가 있었어요. 기대한 만큼 잘 먹지 않아요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L252" s="22" t="n">
@@ -15554,11 +15674,11 @@
         <v>31</v>
       </c>
       <c r="J255" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K255" s="22" t="inlineStr">
         <is>
-          <t>쿠키가 처음부터 잘 먹었어요. 간식 반응이 좋아요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>쿠키에게 권하고 싶지 않아요. 알갱이 크기가 맞지 않아 먹기 불편해해요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L255" s="22" t="n">
@@ -16074,11 +16194,11 @@
         <v>33</v>
       </c>
       <c r="J268" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K268" s="22" t="inlineStr">
         <is>
-          <t>호두가 처음부터 잘 먹었어요. 개별 급여량 관리가 편해요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>호두에게는 맞지 않았어요. 먹고 나서 귀와 발을 계속 핥았어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L268" s="22" t="n">
@@ -16114,11 +16234,11 @@
         <v>33</v>
       </c>
       <c r="J269" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K269" s="22" t="inlineStr">
         <is>
-          <t>보리 반응은 좋은 편이에요. 사료에 섞거나 같이 주기 쉬워요. 조금 더 급여해보고 재구매할 것 같아요.</t>
+          <t>보리 반응은 보통이에요. 다만 급여 후 긁는 횟수가 늘었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L269" s="22" t="n">
@@ -16514,11 +16634,11 @@
         <v>35</v>
       </c>
       <c r="J279" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K279" s="22" t="inlineStr">
         <is>
-          <t>루나가 처음부터 잘 먹었어요. 꾸준히 먹이기 부담 없어요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>루나에게는 맞지 않았어요. 섞어줘도 알아채고 안 먹어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L279" s="22" t="n">
@@ -16594,11 +16714,11 @@
         <v>35</v>
       </c>
       <c r="J281" s="22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K281" s="22" t="inlineStr">
         <is>
-          <t>뭉치가 처음부터 잘 먹었어요. 사료에 섞거나 같이 주기 쉬워요. 전체적으로 만족해서 재구매하려고 합니다.</t>
+          <t>뭉치에게 권하고 싶지 않아요. 급여 자체가 힘들어요. 재구매 의사 없습니다.</t>
         </is>
       </c>
       <c r="L281" s="22" t="n">
@@ -31475,7 +31595,7 @@
       </c>
       <c r="D42" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E42" s="22" t="n">
@@ -31496,7 +31616,7 @@
       </c>
       <c r="D43" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E43" s="22" t="n">
@@ -31517,7 +31637,7 @@
       </c>
       <c r="D44" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E44" s="22" t="n">
@@ -31538,7 +31658,7 @@
       </c>
       <c r="D45" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E45" s="22" t="n">
@@ -33155,7 +33275,7 @@
       </c>
       <c r="D122" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E122" s="22" t="n">
@@ -33176,7 +33296,7 @@
       </c>
       <c r="D123" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E123" s="22" t="n">
@@ -33197,7 +33317,7 @@
       </c>
       <c r="D124" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E124" s="22" t="n">
@@ -33218,7 +33338,7 @@
       </c>
       <c r="D125" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E125" s="22" t="n">
@@ -33239,7 +33359,7 @@
       </c>
       <c r="D126" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E126" s="22" t="n">
@@ -33470,7 +33590,7 @@
       </c>
       <c r="D137" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E137" s="22" t="n">
@@ -34100,7 +34220,7 @@
       </c>
       <c r="D167" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E167" s="22" t="n">
@@ -34520,7 +34640,7 @@
       </c>
       <c r="D187" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E187" s="22" t="n">
@@ -34541,7 +34661,7 @@
       </c>
       <c r="D188" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E188" s="22" t="n">
@@ -34562,7 +34682,7 @@
       </c>
       <c r="D189" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E189" s="22" t="n">
@@ -34583,7 +34703,7 @@
       </c>
       <c r="D190" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E190" s="22" t="n">
@@ -34604,7 +34724,7 @@
       </c>
       <c r="D191" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E191" s="22" t="n">
@@ -35255,7 +35375,7 @@
       </c>
       <c r="D222" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E222" s="22" t="n">
@@ -35276,7 +35396,7 @@
       </c>
       <c r="D223" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E223" s="22" t="n">
@@ -35297,7 +35417,7 @@
       </c>
       <c r="D224" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E224" s="22" t="n">
@@ -35318,7 +35438,7 @@
       </c>
       <c r="D225" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E225" s="22" t="n">
@@ -35339,7 +35459,7 @@
       </c>
       <c r="D226" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E226" s="22" t="n">
@@ -35402,7 +35522,7 @@
       </c>
       <c r="D229" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E229" s="22" t="n">
@@ -35465,7 +35585,7 @@
       </c>
       <c r="D232" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E232" s="22" t="n">
@@ -35885,7 +36005,7 @@
       </c>
       <c r="D252" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E252" s="22" t="n">
@@ -35906,7 +36026,7 @@
       </c>
       <c r="D253" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E253" s="22" t="n">
@@ -35927,7 +36047,7 @@
       </c>
       <c r="D254" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E254" s="22" t="n">
@@ -35948,7 +36068,7 @@
       </c>
       <c r="D255" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E255" s="22" t="n">
@@ -35969,7 +36089,7 @@
       </c>
       <c r="D256" s="22" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E256" s="22" t="n">
@@ -36095,7 +36215,7 @@
       </c>
       <c r="D262" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E262" s="22" t="n">
@@ -36116,7 +36236,7 @@
       </c>
       <c r="D263" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E263" s="22" t="n">
@@ -36137,7 +36257,7 @@
       </c>
       <c r="D264" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E264" s="22" t="n">
@@ -36158,7 +36278,7 @@
       </c>
       <c r="D265" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E265" s="22" t="n">
@@ -36200,7 +36320,7 @@
       </c>
       <c r="D267" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E267" s="22" t="n">
@@ -36221,7 +36341,7 @@
       </c>
       <c r="D268" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E268" s="22" t="n">
@@ -36242,7 +36362,7 @@
       </c>
       <c r="D269" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E269" s="22" t="n">
@@ -36263,7 +36383,7 @@
       </c>
       <c r="D270" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E270" s="22" t="n">
@@ -36284,7 +36404,7 @@
       </c>
       <c r="D271" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E271" s="22" t="n">
@@ -36725,7 +36845,7 @@
       </c>
       <c r="D292" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E292" s="22" t="n">
@@ -37040,7 +37160,7 @@
       </c>
       <c r="D307" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E307" s="22" t="n">
@@ -37061,7 +37181,7 @@
       </c>
       <c r="D308" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E308" s="22" t="n">
@@ -37082,7 +37202,7 @@
       </c>
       <c r="D309" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E309" s="22" t="n">
@@ -37103,7 +37223,7 @@
       </c>
       <c r="D310" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E310" s="22" t="n">
@@ -37124,7 +37244,7 @@
       </c>
       <c r="D311" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E311" s="22" t="n">
@@ -37880,7 +38000,7 @@
       </c>
       <c r="D347" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E347" s="22" t="n">
@@ -38090,7 +38210,7 @@
       </c>
       <c r="D357" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E357" s="22" t="n">
@@ -38111,7 +38231,7 @@
       </c>
       <c r="D358" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E358" s="22" t="n">
@@ -38132,7 +38252,7 @@
       </c>
       <c r="D359" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E359" s="22" t="n">
@@ -38153,7 +38273,7 @@
       </c>
       <c r="D360" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E360" s="22" t="n">
@@ -38174,7 +38294,7 @@
       </c>
       <c r="D361" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E361" s="22" t="n">
@@ -39665,7 +39785,7 @@
       </c>
       <c r="D432" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E432" s="22" t="n">
@@ -40085,7 +40205,7 @@
       </c>
       <c r="D452" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E452" s="22" t="n">
@@ -40106,7 +40226,7 @@
       </c>
       <c r="D453" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E453" s="22" t="n">
@@ -40127,7 +40247,7 @@
       </c>
       <c r="D454" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E454" s="22" t="n">
@@ -40148,7 +40268,7 @@
       </c>
       <c r="D455" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E455" s="22" t="n">
@@ -40169,7 +40289,7 @@
       </c>
       <c r="D456" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E456" s="22" t="n">
@@ -40295,7 +40415,7 @@
       </c>
       <c r="D462" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E462" s="22" t="n">
@@ -40316,7 +40436,7 @@
       </c>
       <c r="D463" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E463" s="22" t="n">
@@ -40337,7 +40457,7 @@
       </c>
       <c r="D464" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E464" s="22" t="n">
@@ -40358,7 +40478,7 @@
       </c>
       <c r="D465" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E465" s="22" t="n">
@@ -41030,7 +41150,7 @@
       </c>
       <c r="D497" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E497" s="22" t="n">
@@ -41051,7 +41171,7 @@
       </c>
       <c r="D498" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E498" s="22" t="n">
@@ -41072,7 +41192,7 @@
       </c>
       <c r="D499" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E499" s="22" t="n">
@@ -41093,7 +41213,7 @@
       </c>
       <c r="D500" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E500" s="22" t="n">
@@ -41114,7 +41234,7 @@
       </c>
       <c r="D501" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E501" s="22" t="n">
@@ -41555,7 +41675,7 @@
       </c>
       <c r="D522" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E522" s="22" t="n">
@@ -41576,7 +41696,7 @@
       </c>
       <c r="D523" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E523" s="22" t="n">
@@ -41597,7 +41717,7 @@
       </c>
       <c r="D524" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E524" s="22" t="n">
@@ -41618,7 +41738,7 @@
       </c>
       <c r="D525" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E525" s="22" t="n">
@@ -41639,7 +41759,7 @@
       </c>
       <c r="D526" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E526" s="22" t="n">
@@ -42080,7 +42200,7 @@
       </c>
       <c r="D547" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E547" s="22" t="n">
@@ -42101,7 +42221,7 @@
       </c>
       <c r="D548" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E548" s="22" t="n">
@@ -42122,7 +42242,7 @@
       </c>
       <c r="D549" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E549" s="22" t="n">
@@ -42143,7 +42263,7 @@
       </c>
       <c r="D550" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E550" s="22" t="n">
@@ -42227,7 +42347,7 @@
       </c>
       <c r="D554" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E554" s="22" t="n">
@@ -42248,7 +42368,7 @@
       </c>
       <c r="D555" s="22" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E555" s="22" t="n">
@@ -42269,7 +42389,7 @@
       </c>
       <c r="D556" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E556" s="22" t="n">
@@ -42395,7 +42515,7 @@
       </c>
       <c r="D562" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E562" s="22" t="n">
@@ -42500,7 +42620,7 @@
       </c>
       <c r="D567" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E567" s="22" t="n">
@@ -42521,7 +42641,7 @@
       </c>
       <c r="D568" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E568" s="22" t="n">
@@ -42542,7 +42662,7 @@
       </c>
       <c r="D569" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E569" s="22" t="n">
@@ -42563,7 +42683,7 @@
       </c>
       <c r="D570" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E570" s="22" t="n">
@@ -42584,7 +42704,7 @@
       </c>
       <c r="D571" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E571" s="22" t="n">
@@ -43550,7 +43670,7 @@
       </c>
       <c r="D617" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E617" s="22" t="n">
@@ -43571,7 +43691,7 @@
       </c>
       <c r="D618" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E618" s="22" t="n">
@@ -43592,7 +43712,7 @@
       </c>
       <c r="D619" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E619" s="22" t="n">
@@ -43613,7 +43733,7 @@
       </c>
       <c r="D620" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E620" s="22" t="n">
@@ -43634,7 +43754,7 @@
       </c>
       <c r="D621" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E621" s="22" t="n">
@@ -44705,7 +44825,7 @@
       </c>
       <c r="D672" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E672" s="22" t="n">
@@ -44726,7 +44846,7 @@
       </c>
       <c r="D673" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E673" s="22" t="n">
@@ -44747,7 +44867,7 @@
       </c>
       <c r="D674" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E674" s="22" t="n">
@@ -44768,7 +44888,7 @@
       </c>
       <c r="D675" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E675" s="22" t="n">
@@ -44789,7 +44909,7 @@
       </c>
       <c r="D676" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E676" s="22" t="n">
@@ -44831,7 +44951,7 @@
       </c>
       <c r="D678" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E678" s="22" t="n">
@@ -45125,7 +45245,7 @@
       </c>
       <c r="D692" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E692" s="22" t="n">
@@ -45146,7 +45266,7 @@
       </c>
       <c r="D693" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E693" s="22" t="n">
@@ -45167,7 +45287,7 @@
       </c>
       <c r="D694" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E694" s="22" t="n">
@@ -45188,7 +45308,7 @@
       </c>
       <c r="D695" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E695" s="22" t="n">
@@ -45335,7 +45455,7 @@
       </c>
       <c r="D702" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E702" s="22" t="n">
@@ -45356,7 +45476,7 @@
       </c>
       <c r="D703" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E703" s="22" t="n">
@@ -45377,7 +45497,7 @@
       </c>
       <c r="D704" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E704" s="22" t="n">
@@ -45398,7 +45518,7 @@
       </c>
       <c r="D705" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E705" s="22" t="n">
@@ -45419,7 +45539,7 @@
       </c>
       <c r="D706" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E706" s="22" t="n">
@@ -46175,7 +46295,7 @@
       </c>
       <c r="D742" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E742" s="22" t="n">
@@ -46196,7 +46316,7 @@
       </c>
       <c r="D743" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E743" s="22" t="n">
@@ -46217,7 +46337,7 @@
       </c>
       <c r="D744" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E744" s="22" t="n">
@@ -46238,7 +46358,7 @@
       </c>
       <c r="D745" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E745" s="22" t="n">
@@ -46259,7 +46379,7 @@
       </c>
       <c r="D746" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E746" s="22" t="n">
@@ -46385,7 +46505,7 @@
       </c>
       <c r="D752" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E752" s="22" t="n">
@@ -46406,7 +46526,7 @@
       </c>
       <c r="D753" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E753" s="22" t="n">
@@ -46427,7 +46547,7 @@
       </c>
       <c r="D754" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E754" s="22" t="n">
@@ -46448,7 +46568,7 @@
       </c>
       <c r="D755" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E755" s="22" t="n">
@@ -46532,7 +46652,7 @@
       </c>
       <c r="D759" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E759" s="22" t="n">
@@ -49010,7 +49130,7 @@
       </c>
       <c r="D877" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E877" s="22" t="n">
@@ -49031,7 +49151,7 @@
       </c>
       <c r="D878" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E878" s="22" t="n">
@@ -49052,7 +49172,7 @@
       </c>
       <c r="D879" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E879" s="22" t="n">
@@ -49073,7 +49193,7 @@
       </c>
       <c r="D880" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E880" s="22" t="n">
@@ -49220,7 +49340,7 @@
       </c>
       <c r="D887" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E887" s="22" t="n">
@@ -49241,7 +49361,7 @@
       </c>
       <c r="D888" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E888" s="22" t="n">
@@ -49262,7 +49382,7 @@
       </c>
       <c r="D889" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E889" s="22" t="n">
@@ -49283,7 +49403,7 @@
       </c>
       <c r="D890" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E890" s="22" t="n">
@@ -51530,7 +51650,7 @@
       </c>
       <c r="D997" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E997" s="22" t="n">
@@ -51551,7 +51671,7 @@
       </c>
       <c r="D998" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E998" s="22" t="n">
@@ -51572,7 +51692,7 @@
       </c>
       <c r="D999" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E999" s="22" t="n">
@@ -51593,7 +51713,7 @@
       </c>
       <c r="D1000" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1000" s="22" t="n">
@@ -51614,7 +51734,7 @@
       </c>
       <c r="D1001" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1001" s="22" t="n">
@@ -51635,7 +51755,7 @@
       </c>
       <c r="D1002" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1002" s="22" t="n">
@@ -52055,7 +52175,7 @@
       </c>
       <c r="D1022" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1022" s="22" t="n">
@@ -53630,7 +53750,7 @@
       </c>
       <c r="D1097" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1097" s="22" t="n">
@@ -53651,7 +53771,7 @@
       </c>
       <c r="D1098" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1098" s="22" t="n">
@@ -53672,7 +53792,7 @@
       </c>
       <c r="D1099" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1099" s="22" t="n">
@@ -53693,7 +53813,7 @@
       </c>
       <c r="D1100" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1100" s="22" t="n">
@@ -53714,7 +53834,7 @@
       </c>
       <c r="D1101" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1101" s="22" t="n">
@@ -53945,7 +54065,7 @@
       </c>
       <c r="D1112" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1112" s="22" t="n">
@@ -53966,7 +54086,7 @@
       </c>
       <c r="D1113" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1113" s="22" t="n">
@@ -53987,7 +54107,7 @@
       </c>
       <c r="D1114" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1114" s="22" t="n">
@@ -54008,7 +54128,7 @@
       </c>
       <c r="D1115" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1115" s="22" t="n">
@@ -54029,7 +54149,7 @@
       </c>
       <c r="D1116" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1116" s="22" t="n">
@@ -55835,7 +55955,7 @@
       </c>
       <c r="D1202" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1202" s="22" t="n">
@@ -55856,7 +55976,7 @@
       </c>
       <c r="D1203" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1203" s="22" t="n">
@@ -55877,7 +55997,7 @@
       </c>
       <c r="D1204" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1204" s="22" t="n">
@@ -55898,7 +56018,7 @@
       </c>
       <c r="D1205" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1205" s="22" t="n">
@@ -56255,7 +56375,7 @@
       </c>
       <c r="D1222" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1222" s="22" t="n">
@@ -56276,7 +56396,7 @@
       </c>
       <c r="D1223" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1223" s="22" t="n">
@@ -56297,7 +56417,7 @@
       </c>
       <c r="D1224" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1224" s="22" t="n">
@@ -56318,7 +56438,7 @@
       </c>
       <c r="D1225" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1225" s="22" t="n">
@@ -56885,7 +57005,7 @@
       </c>
       <c r="D1252" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1252" s="22" t="n">
@@ -56906,7 +57026,7 @@
       </c>
       <c r="D1253" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1253" s="22" t="n">
@@ -56927,7 +57047,7 @@
       </c>
       <c r="D1254" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1254" s="22" t="n">
@@ -56948,7 +57068,7 @@
       </c>
       <c r="D1255" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1255" s="22" t="n">
@@ -56969,7 +57089,7 @@
       </c>
       <c r="D1256" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1256" s="22" t="n">
@@ -57200,7 +57320,7 @@
       </c>
       <c r="D1267" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1267" s="22" t="n">
@@ -57221,7 +57341,7 @@
       </c>
       <c r="D1268" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1268" s="22" t="n">
@@ -57242,7 +57362,7 @@
       </c>
       <c r="D1269" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1269" s="22" t="n">
@@ -57263,7 +57383,7 @@
       </c>
       <c r="D1270" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1270" s="22" t="n">
@@ -57284,7 +57404,7 @@
       </c>
       <c r="D1271" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1271" s="22" t="n">
@@ -58565,7 +58685,7 @@
       </c>
       <c r="D1332" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1332" s="22" t="n">
@@ -58586,7 +58706,7 @@
       </c>
       <c r="D1333" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1333" s="22" t="n">
@@ -58607,7 +58727,7 @@
       </c>
       <c r="D1334" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1334" s="22" t="n">
@@ -58628,7 +58748,7 @@
       </c>
       <c r="D1335" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1335" s="22" t="n">
@@ -58649,7 +58769,7 @@
       </c>
       <c r="D1336" s="22" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1336" s="22" t="n">
@@ -59720,7 +59840,7 @@
       </c>
       <c r="D1387" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1387" s="22" t="n">
@@ -59741,7 +59861,7 @@
       </c>
       <c r="D1388" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1388" s="22" t="n">
@@ -59762,7 +59882,7 @@
       </c>
       <c r="D1389" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1389" s="22" t="n">
@@ -59783,7 +59903,7 @@
       </c>
       <c r="D1390" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1390" s="22" t="n">
@@ -59930,7 +60050,7 @@
       </c>
       <c r="D1397" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1397" s="22" t="n">
@@ -59951,7 +60071,7 @@
       </c>
       <c r="D1398" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1398" s="22" t="n">
@@ -59972,7 +60092,7 @@
       </c>
       <c r="D1399" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEGATIVE</t>
         </is>
       </c>
       <c r="E1399" s="22" t="n">
@@ -59993,7 +60113,7 @@
       </c>
       <c r="D1400" s="22" t="inlineStr">
         <is>
-          <t>POSITIVE</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E1400" s="22" t="n">
@@ -66941,10 +67061,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="22" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="G2" s="22" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="H2" s="22" t="inlineStr">
         <is>
@@ -67025,10 +67145,10 @@
         <v>8</v>
       </c>
       <c r="F4" s="22" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="G4" s="22" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="22" t="inlineStr">
         <is>
@@ -67067,10 +67187,10 @@
         <v>7</v>
       </c>
       <c r="F5" s="22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G5" s="22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
@@ -67109,10 +67229,10 @@
         <v>8</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
@@ -67151,10 +67271,10 @@
         <v>6</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
@@ -67193,10 +67313,10 @@
         <v>10</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
@@ -67235,10 +67355,10 @@
         <v>7</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="H9" s="22" t="inlineStr">
         <is>
@@ -67277,10 +67397,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="H10" s="22" t="inlineStr">
         <is>
@@ -67403,10 +67523,10 @@
         <v>6</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
@@ -67445,10 +67565,10 @@
         <v>15</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
@@ -67487,10 +67607,10 @@
         <v>10</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
@@ -67529,10 +67649,10 @@
         <v>9</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="H16" s="22" t="inlineStr">
         <is>
@@ -67571,10 +67691,10 @@
         <v>11</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
@@ -67613,10 +67733,10 @@
         <v>11</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
@@ -67655,10 +67775,10 @@
         <v>7</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="H19" s="22" t="inlineStr">
         <is>
@@ -67697,10 +67817,10 @@
         <v>8</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
@@ -67739,10 +67859,10 @@
         <v>9</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H21" s="22" t="inlineStr">
         <is>
@@ -67781,10 +67901,10 @@
         <v>8</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
@@ -67823,10 +67943,10 @@
         <v>6</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="H23" s="22" t="inlineStr">
         <is>
@@ -67949,10 +68069,10 @@
         <v>13</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="G26" s="22" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="H26" s="22" t="inlineStr">
         <is>
@@ -68033,10 +68153,10 @@
         <v>11</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="H28" s="22" t="inlineStr">
         <is>
@@ -68159,10 +68279,10 @@
         <v>7</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="G31" s="22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="H31" s="22" t="inlineStr">
         <is>
@@ -68201,10 +68321,10 @@
         <v>8</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H32" s="22" t="inlineStr">
         <is>
@@ -68285,10 +68405,10 @@
         <v>5</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="G34" s="22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="H34" s="22" t="inlineStr">
         <is>
@@ -68369,10 +68489,10 @@
         <v>7</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="G36" s="22" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="H36" s="22" t="inlineStr">
         <is>
@@ -71723,7 +71843,7 @@
         <v>8268</v>
       </c>
       <c r="O2" s="41" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="P2" s="22" t="n">
         <v>12</v>
@@ -71993,7 +72113,7 @@
         <v>10348</v>
       </c>
       <c r="O4" s="41" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P4" s="22" t="n">
         <v>8</v>
@@ -72128,7 +72248,7 @@
         <v>11388</v>
       </c>
       <c r="O5" s="41" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P5" s="22" t="n">
         <v>7</v>
@@ -72263,7 +72383,7 @@
         <v>2860</v>
       </c>
       <c r="O6" s="41" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P6" s="22" t="n">
         <v>8</v>
@@ -72398,7 +72518,7 @@
         <v>3588</v>
       </c>
       <c r="O7" s="41" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="P7" s="22" t="n">
         <v>6</v>
@@ -72533,7 +72653,7 @@
         <v>3380</v>
       </c>
       <c r="O8" s="41" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="P8" s="22" t="n">
         <v>10</v>
@@ -72668,7 +72788,7 @@
         <v>3068</v>
       </c>
       <c r="O9" s="41" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="P9" s="22" t="n">
         <v>7</v>
@@ -72803,7 +72923,7 @@
         <v>7748</v>
       </c>
       <c r="O10" s="41" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P10" s="22" t="n">
         <v>5</v>
@@ -73208,7 +73328,7 @@
         <v>8788</v>
       </c>
       <c r="O13" s="41" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P13" s="22" t="n">
         <v>6</v>
@@ -73343,7 +73463,7 @@
         <v>12428</v>
       </c>
       <c r="O14" s="41" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="P14" s="22" t="n">
         <v>15</v>
@@ -73478,7 +73598,7 @@
         <v>13468</v>
       </c>
       <c r="O15" s="41" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P15" s="22" t="n">
         <v>10</v>
@@ -73613,7 +73733,7 @@
         <v>13988</v>
       </c>
       <c r="O16" s="41" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="P16" s="22" t="n">
         <v>9</v>
@@ -73748,7 +73868,7 @@
         <v>15028</v>
       </c>
       <c r="O17" s="41" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P17" s="22" t="n">
         <v>11</v>
@@ -73883,7 +74003,7 @@
         <v>4108</v>
       </c>
       <c r="O18" s="41" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="P18" s="22" t="n">
         <v>11</v>
@@ -74018,7 +74138,7 @@
         <v>5148</v>
       </c>
       <c r="O19" s="41" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="P19" s="22" t="n">
         <v>7</v>
@@ -74153,7 +74273,7 @@
         <v>4420</v>
       </c>
       <c r="O20" s="41" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P20" s="22" t="n">
         <v>8</v>
@@ -74288,7 +74408,7 @@
         <v>4784</v>
       </c>
       <c r="O21" s="41" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P21" s="22" t="n">
         <v>9</v>
@@ -74423,7 +74543,7 @@
         <v>11388</v>
       </c>
       <c r="O22" s="41" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="P22" s="22" t="n">
         <v>8</v>
@@ -74558,7 +74678,7 @@
         <v>10348</v>
       </c>
       <c r="O23" s="41" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P23" s="22" t="n">
         <v>6</v>
@@ -74959,7 +75079,7 @@
         <v>14508</v>
       </c>
       <c r="O26" s="41" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P26" s="22" t="n">
         <v>13</v>
@@ -75221,7 +75341,7 @@
         <v>13988</v>
       </c>
       <c r="O28" s="41" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="P28" s="22" t="n">
         <v>11</v>
@@ -75614,7 +75734,7 @@
         <v>3068</v>
       </c>
       <c r="O31" s="41" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P31" s="22" t="n">
         <v>7</v>
@@ -75745,7 +75865,7 @@
         <v>3952</v>
       </c>
       <c r="O32" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P32" s="22" t="n">
         <v>8</v>
@@ -76007,7 +76127,7 @@
         <v>9308</v>
       </c>
       <c r="O34" s="41" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P34" s="22" t="n">
         <v>5</v>
@@ -76269,7 +76389,7 @@
         <v>9828</v>
       </c>
       <c r="O36" s="41" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="P36" s="22" t="n">
         <v>7</v>

--- a/data/mock/상품 목데이터/golajulgaenyang_full_schema_mockdata_product_thumbnails_linked.xlsx
+++ b/data/mock/상품 목데이터/golajulgaenyang_full_schema_mockdata_product_thumbnails_linked.xlsx
@@ -5838,7 +5838,7 @@
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>보리 반응은 보통이에요. 다만 사료를 거의 먹지 않고 남겼어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>보리 반응은 보통이에요. 다만 처음보다 먹는 양이 조금 줄었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L9" s="22" t="n">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="K29" s="22" t="inlineStr">
         <is>
-          <t>두부 반응은 보통이에요. 다만 사료를 거의 먹지 않고 남겼어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>두부 반응은 보통이에요. 다만 처음보다 먹는 양이 조금 줄었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L29" s="22" t="n">
@@ -6878,7 +6878,7 @@
       </c>
       <c r="K35" s="22" t="inlineStr">
         <is>
-          <t>몽이에게는 그냥 무난한 정도였어요. 다만 냄새를 맡고 고개를 돌려요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>몽이에게는 그냥 무난한 정도였어요. 다만 잘 먹을 때도 있고 남길 때도 있어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L35" s="22" t="n">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="K47" s="22" t="inlineStr">
         <is>
-          <t>탄이 반응은 보통이에요. 다만 소분이 어렵고 흘리기 쉬워요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>탄이 반응은 보통이에요. 다만 소분이 약간 번거로워요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L47" s="22" t="n">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="K48" s="22" t="inlineStr">
         <is>
-          <t>몽이에게는 그냥 무난한 정도였어요. 다만 한두 번 먹고 더는 안 먹으려 해요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>몽이에게는 그냥 무난한 정도였어요. 다만 좋아하는 날도 있고 시큰둥한 날도 있어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L48" s="22" t="n">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="K60" s="22" t="inlineStr">
         <is>
-          <t>탄이에게는 그냥 무난한 정도였어요. 다만 간식인데도 관심을 보이지 않아요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>탄이에게는 그냥 무난한 정도였어요. 다만 간식 반응이 그리 크지 않았어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L60" s="22" t="n">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="K61" s="22" t="inlineStr">
         <is>
-          <t>호두 반응은 보통이에요. 다만 한두 번 먹고 더는 안 먹으려 해요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>호두 반응은 보통이에요. 다만 좋아하는 날도 있고 시큰둥한 날도 있어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L61" s="22" t="n">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="K71" s="22" t="inlineStr">
         <is>
-          <t>루이 반응은 보통이에요. 다만 급여 자체가 힘들어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>루이 반응은 보통이에요. 다만 급여 반응이 들쭉날쭉해요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L71" s="22" t="n">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="K88" s="22" t="inlineStr">
         <is>
-          <t>모찌 반응은 보통이에요. 다만 영양제를 먹이려고 하면 피해요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>모찌 반응은 보통이에요. 다만 먹이는 데 약간 손이 가요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L88" s="22" t="n">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="K114" s="22" t="inlineStr">
         <is>
-          <t>구름 반응은 보통이에요. 다만 기존 사료보다 먹는 양이 확 줄었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>구름 반응은 보통이에요. 다만 기호성은 그저 그런 편이에요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L114" s="22" t="n">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="K120" s="22" t="inlineStr">
         <is>
-          <t>구름 반응은 보통이에요. 다만 사료를 거의 먹지 않고 남겼어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>구름 반응은 보통이에요. 다만 처음보다 먹는 양이 조금 줄었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L120" s="22" t="n">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="K137" s="22" t="inlineStr">
         <is>
-          <t>탄이 반응은 보통이에요. 다만 먹고 나서 배변 상태가 안 좋아졌어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>탄이 반응은 보통이에요. 다만 배변 변화는 뚜렷하지 않았어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L137" s="22" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="K153" s="22" t="inlineStr">
         <is>
-          <t>두부 반응은 보통이에요. 다만 포장이 불편해서 급여하기 어려워요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>두부 반응은 보통이에요. 다만 포장이 조금 불편했어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L153" s="22" t="n">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="K165" s="22" t="inlineStr">
         <is>
-          <t>루이 반응은 보통이에요. 다만 알레르기 반응이 의심돼서 중단했어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>루이 반응은 보통이에요. 다만 알레르기 반응은 없었지만 큰 변화도 없었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L165" s="22" t="n">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K176" s="22" t="inlineStr">
         <is>
-          <t>보리에게는 그냥 무난한 정도였어요. 다만 섞어줘도 알아채고 안 먹어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>보리에게는 그냥 무난한 정도였어요. 다만 간식에 섞으면 먹지만 그냥은 잘 안 먹어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L176" s="22" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="K202" s="22" t="inlineStr">
         <is>
-          <t>두부에게는 그냥 무난한 정도였어요. 다만 냄새를 맡고 고개를 돌려요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>두부에게는 그냥 무난한 정도였어요. 다만 잘 먹을 때도 있고 남길 때도 있어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L202" s="22" t="n">
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K206" s="22" t="inlineStr">
         <is>
-          <t>마루 반응은 보통이에요. 다만 기존 사료보다 먹는 양이 확 줄었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>마루 반응은 보통이에요. 다만 기호성은 그저 그런 편이에요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L206" s="22" t="n">
@@ -16238,7 +16238,7 @@
       </c>
       <c r="K269" s="22" t="inlineStr">
         <is>
-          <t>보리 반응은 보통이에요. 다만 급여 후 긁는 횟수가 늘었어요. 조금 더 먹여보고 결정할 것 같아요.</t>
+          <t>보리 반응은 보통이에요. 다만 피부나 모질 변화는 아직 잘 모르겠어요. 조금 더 먹여보고 결정할 것 같아요.</t>
         </is>
       </c>
       <c r="L269" s="22" t="n">

--- a/data/mock/상품 목데이터/golajulgaenyang_full_schema_mockdata_product_thumbnails_linked.xlsx
+++ b/data/mock/상품 목데이터/golajulgaenyang_full_schema_mockdata_product_thumbnails_linked.xlsx
@@ -14,7 +14,7 @@
     <sheet name="product_cautions" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="product_ingredients" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="inventories" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="stock_events" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="stock_movements" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="review" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="review_pet" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="review_health_concern" sheetId="15" state="visible" r:id="rId15"/>
@@ -1787,6 +1787,7 @@
       <c r="G1" s="21" t="n"/>
       <c r="H1" s="21" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>

--- a/data/mock/상품 목데이터/golajulgaenyang_full_schema_mockdata_product_thumbnails_linked.xlsx
+++ b/data/mock/상품 목데이터/golajulgaenyang_full_schema_mockdata_product_thumbnails_linked.xlsx
@@ -1766,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="18" min="1" max="1"/>
@@ -1787,7 +1787,6 @@
       <c r="G1" s="21" t="n"/>
       <c r="H1" s="21" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -1929,6 +1928,18 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>현실적인 J자형 분포로 조정 (5점 180 / 4점 55 / 3점 18 / 2점 10 / 1점 24). 1~2점 리뷰는 review_question.review_answer 에 NEGATIVE 값 사용 (기존 POSITIVE/NEUTRAL 에 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>리뷰 질문 유형</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>리뷰당 6개 구조화 질문 응답 (PALATABILITY/DIGESTION/FEEDING_CONVENIENCE/SKIN_COAT/WEIGHT_VITALITY/ALLERGY)</t>
         </is>
       </c>
     </row>
@@ -30705,7 +30716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1436"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" style="18" min="1" max="1"/>
@@ -60874,6 +60885,6033 @@
         </is>
       </c>
       <c r="E1436" s="22" t="n">
+        <v>46274.125</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="n">
+        <v>1436</v>
+      </c>
+      <c r="B1437" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1437" t="n">
+        <v>46279.33333333334</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B1438" t="n">
+        <v>2</v>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1438" t="n">
+        <v>46279.41666666666</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="n">
+        <v>1438</v>
+      </c>
+      <c r="B1439" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1439" t="n">
+        <v>46276.20833333334</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="n">
+        <v>1439</v>
+      </c>
+      <c r="B1440" t="n">
+        <v>4</v>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1440" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="n">
+        <v>1440</v>
+      </c>
+      <c r="B1441" t="n">
+        <v>5</v>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1441" t="n">
+        <v>46282.375</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B1442" t="n">
+        <v>6</v>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1442" t="n">
+        <v>46278.125</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="n">
+        <v>1442</v>
+      </c>
+      <c r="B1443" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1443" t="n">
+        <v>46281.375</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="n">
+        <v>1443</v>
+      </c>
+      <c r="B1444" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1444" t="n">
+        <v>46272.125</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="n">
+        <v>1444</v>
+      </c>
+      <c r="B1445" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1445" t="n">
+        <v>46292.41666666666</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="n">
+        <v>1445</v>
+      </c>
+      <c r="B1446" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1446" t="n">
+        <v>46284.20833333334</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="n">
+        <v>1446</v>
+      </c>
+      <c r="B1447" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1447" t="n">
+        <v>46279.16666666666</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B1448" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1448" t="n">
+        <v>46292.41666666666</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="n">
+        <v>1448</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1449" t="n">
+        <v>46267.20833333334</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="n">
+        <v>1449</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1450" t="n">
+        <v>46293.375</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="n">
+        <v>1450</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1451" t="n">
+        <v>46290.08333333334</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="n">
+        <v>1451</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1452" t="n">
+        <v>46269.08333333334</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="n">
+        <v>1452</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1453" t="n">
+        <v>46270.08333333334</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="n">
+        <v>1453</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1454" t="n">
+        <v>46288.20833333334</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B1455" t="n">
+        <v>19</v>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1455" t="n">
+        <v>46280.33333333334</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="n">
+        <v>1455</v>
+      </c>
+      <c r="B1456" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1456" t="n">
+        <v>46279.375</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="n">
+        <v>1456</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>21</v>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1457" t="n">
+        <v>46276.375</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B1458" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1458" t="n">
+        <v>46268.08333333334</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="n">
+        <v>1458</v>
+      </c>
+      <c r="B1459" t="n">
+        <v>23</v>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1459" t="n">
+        <v>46281.29166666666</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="n">
+        <v>1459</v>
+      </c>
+      <c r="B1460" t="n">
+        <v>24</v>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1460" t="n">
+        <v>46290.33333333334</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="n">
+        <v>1460</v>
+      </c>
+      <c r="B1461" t="n">
+        <v>25</v>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1461" t="n">
+        <v>46279.29166666666</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="n">
+        <v>1461</v>
+      </c>
+      <c r="B1462" t="n">
+        <v>26</v>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1462" t="n">
+        <v>46276.375</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="n">
+        <v>1462</v>
+      </c>
+      <c r="B1463" t="n">
+        <v>27</v>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1463" t="n">
+        <v>46291.125</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="n">
+        <v>1463</v>
+      </c>
+      <c r="B1464" t="n">
+        <v>28</v>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1464" t="n">
+        <v>46274.41666666666</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="n">
+        <v>1464</v>
+      </c>
+      <c r="B1465" t="n">
+        <v>29</v>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1465" t="n">
+        <v>46284.29166666666</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="n">
+        <v>1465</v>
+      </c>
+      <c r="B1466" t="n">
+        <v>30</v>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1466" t="n">
+        <v>46284.29166666666</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="n">
+        <v>1466</v>
+      </c>
+      <c r="B1467" t="n">
+        <v>31</v>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1467" t="n">
+        <v>46267.29166666666</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B1468" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1468" t="n">
+        <v>46288.33333333334</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="n">
+        <v>1468</v>
+      </c>
+      <c r="B1469" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1469" t="n">
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="n">
+        <v>1469</v>
+      </c>
+      <c r="B1470" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1470" t="n">
+        <v>46285.125</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="n">
+        <v>1470</v>
+      </c>
+      <c r="B1471" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1471" t="n">
+        <v>46266.41666666666</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B1472" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1472" t="n">
+        <v>46270.16666666666</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="n">
+        <v>1472</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1473" t="n">
+        <v>46290.04166666666</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1474" t="n">
+        <v>46270.29166666666</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="n">
+        <v>1474</v>
+      </c>
+      <c r="B1475" t="n">
+        <v>39</v>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1475" t="n">
+        <v>46282.375</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="n">
+        <v>1475</v>
+      </c>
+      <c r="B1476" t="n">
+        <v>40</v>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1476" t="n">
+        <v>46288.33333333334</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="n">
+        <v>1476</v>
+      </c>
+      <c r="B1477" t="n">
+        <v>41</v>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1477" t="n">
+        <v>46275.375</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="n">
+        <v>1477</v>
+      </c>
+      <c r="B1478" t="n">
+        <v>42</v>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1478" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="n">
+        <v>1478</v>
+      </c>
+      <c r="B1479" t="n">
+        <v>43</v>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1479" t="n">
+        <v>46275.33333333334</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="n">
+        <v>1479</v>
+      </c>
+      <c r="B1480" t="n">
+        <v>44</v>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1480" t="n">
+        <v>46269.41666666666</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="n">
+        <v>1480</v>
+      </c>
+      <c r="B1481" t="n">
+        <v>45</v>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1481" t="n">
+        <v>46276.375</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="n">
+        <v>1481</v>
+      </c>
+      <c r="B1482" t="n">
+        <v>46</v>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1482" t="n">
+        <v>46282.16666666666</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="n">
+        <v>1482</v>
+      </c>
+      <c r="B1483" t="n">
+        <v>47</v>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1483" t="n">
+        <v>46269.29166666666</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="n">
+        <v>1483</v>
+      </c>
+      <c r="B1484" t="n">
+        <v>48</v>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1484" t="n">
+        <v>46274.16666666666</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="n">
+        <v>1484</v>
+      </c>
+      <c r="B1485" t="n">
+        <v>49</v>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1485" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="n">
+        <v>1485</v>
+      </c>
+      <c r="B1486" t="n">
+        <v>50</v>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1486" t="n">
+        <v>46273.375</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="n">
+        <v>1486</v>
+      </c>
+      <c r="B1487" t="n">
+        <v>51</v>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1487" t="n">
+        <v>46291.125</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="n">
+        <v>1487</v>
+      </c>
+      <c r="B1488" t="n">
+        <v>52</v>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1488" t="n">
+        <v>46267.33333333334</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="n">
+        <v>1488</v>
+      </c>
+      <c r="B1489" t="n">
+        <v>53</v>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1489" t="n">
+        <v>46266.29166666666</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="n">
+        <v>1489</v>
+      </c>
+      <c r="B1490" t="n">
+        <v>54</v>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1490" t="n">
+        <v>46277.33333333334</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="n">
+        <v>1490</v>
+      </c>
+      <c r="B1491" t="n">
+        <v>55</v>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1491" t="n">
+        <v>46287.25</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="n">
+        <v>1491</v>
+      </c>
+      <c r="B1492" t="n">
+        <v>56</v>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1492" t="n">
+        <v>46284.04166666666</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="n">
+        <v>1492</v>
+      </c>
+      <c r="B1493" t="n">
+        <v>57</v>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1493" t="n">
+        <v>46271.33333333334</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="n">
+        <v>1493</v>
+      </c>
+      <c r="B1494" t="n">
+        <v>58</v>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1494" t="n">
+        <v>46281.16666666666</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="n">
+        <v>1494</v>
+      </c>
+      <c r="B1495" t="n">
+        <v>59</v>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1495" t="n">
+        <v>46283.25</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="n">
+        <v>1495</v>
+      </c>
+      <c r="B1496" t="n">
+        <v>60</v>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1496" t="n">
+        <v>46278.08333333334</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="n">
+        <v>1496</v>
+      </c>
+      <c r="B1497" t="n">
+        <v>61</v>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1497" t="n">
+        <v>46284.41666666666</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B1498" t="n">
+        <v>62</v>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1498" t="n">
+        <v>46283.08333333334</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="n">
+        <v>1498</v>
+      </c>
+      <c r="B1499" t="n">
+        <v>63</v>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1499" t="n">
+        <v>46271.29166666666</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="n">
+        <v>1499</v>
+      </c>
+      <c r="B1500" t="n">
+        <v>64</v>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1500" t="n">
+        <v>46285.04166666666</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B1501" t="n">
+        <v>65</v>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1501" t="n">
+        <v>46279.41666666666</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B1502" t="n">
+        <v>66</v>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1502" t="n">
+        <v>46273.33333333334</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B1503" t="n">
+        <v>67</v>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1503" t="n">
+        <v>46275.20833333334</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B1504" t="n">
+        <v>68</v>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1504" t="n">
+        <v>46275.25</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B1505" t="n">
+        <v>69</v>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1505" t="n">
+        <v>46279.375</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B1506" t="n">
+        <v>70</v>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1506" t="n">
+        <v>46273.375</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B1507" t="n">
+        <v>71</v>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1507" t="n">
+        <v>46283.25</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B1508" t="n">
+        <v>72</v>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1508" t="n">
+        <v>46277.04166666666</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B1509" t="n">
+        <v>73</v>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1509" t="n">
+        <v>46273.33333333334</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B1510" t="n">
+        <v>74</v>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1510" t="n">
+        <v>46269.08333333334</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="n">
+        <v>1510</v>
+      </c>
+      <c r="B1511" t="n">
+        <v>75</v>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1511" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B1512" t="n">
+        <v>76</v>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1512" t="n">
+        <v>46288.29166666666</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B1513" t="n">
+        <v>77</v>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1513" t="n">
+        <v>46292.125</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="n">
+        <v>1513</v>
+      </c>
+      <c r="B1514" t="n">
+        <v>78</v>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1514" t="n">
+        <v>46278.04166666666</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="n">
+        <v>1514</v>
+      </c>
+      <c r="B1515" t="n">
+        <v>79</v>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1515" t="n">
+        <v>46288.33333333334</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B1516" t="n">
+        <v>80</v>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1516" t="n">
+        <v>46268.04166666666</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B1517" t="n">
+        <v>81</v>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1517" t="n">
+        <v>46291.125</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="n">
+        <v>1517</v>
+      </c>
+      <c r="B1518" t="n">
+        <v>82</v>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1518" t="n">
+        <v>46275.04166666666</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="n">
+        <v>1518</v>
+      </c>
+      <c r="B1519" t="n">
+        <v>83</v>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1519" t="n">
+        <v>46291.41666666666</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B1520" t="n">
+        <v>84</v>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1520" t="n">
+        <v>46275.25</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="n">
+        <v>1520</v>
+      </c>
+      <c r="B1521" t="n">
+        <v>85</v>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1521" t="n">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="n">
+        <v>1521</v>
+      </c>
+      <c r="B1522" t="n">
+        <v>86</v>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1522" t="n">
+        <v>46288.16666666666</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B1523" t="n">
+        <v>87</v>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1523" t="n">
+        <v>46288.41666666666</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="n">
+        <v>1523</v>
+      </c>
+      <c r="B1524" t="n">
+        <v>88</v>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1524" t="n">
+        <v>46271.16666666666</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="n">
+        <v>1524</v>
+      </c>
+      <c r="B1525" t="n">
+        <v>89</v>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1525" t="n">
+        <v>46277.125</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="n">
+        <v>1525</v>
+      </c>
+      <c r="B1526" t="n">
+        <v>90</v>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1526" t="n">
+        <v>46270.29166666666</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="n">
+        <v>1526</v>
+      </c>
+      <c r="B1527" t="n">
+        <v>91</v>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1527" t="n">
+        <v>46277.20833333334</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="n">
+        <v>1527</v>
+      </c>
+      <c r="B1528" t="n">
+        <v>92</v>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1528" t="n">
+        <v>46282.16666666666</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="n">
+        <v>1528</v>
+      </c>
+      <c r="B1529" t="n">
+        <v>93</v>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1529" t="n">
+        <v>46293.25</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="n">
+        <v>1529</v>
+      </c>
+      <c r="B1530" t="n">
+        <v>94</v>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1530" t="n">
+        <v>46278.25</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="n">
+        <v>1530</v>
+      </c>
+      <c r="B1531" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1531" t="n">
+        <v>46279.125</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="n">
+        <v>1531</v>
+      </c>
+      <c r="B1532" t="n">
+        <v>96</v>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1532" t="n">
+        <v>46291.25</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="n">
+        <v>1532</v>
+      </c>
+      <c r="B1533" t="n">
+        <v>97</v>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1533" t="n">
+        <v>46293.33333333334</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="n">
+        <v>1533</v>
+      </c>
+      <c r="B1534" t="n">
+        <v>98</v>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1534" t="n">
+        <v>46288.41666666666</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="n">
+        <v>1534</v>
+      </c>
+      <c r="B1535" t="n">
+        <v>99</v>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1535" t="n">
+        <v>46274.29166666666</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="n">
+        <v>1535</v>
+      </c>
+      <c r="B1536" t="n">
+        <v>100</v>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1536" t="n">
+        <v>46275.16666666666</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="n">
+        <v>1536</v>
+      </c>
+      <c r="B1537" t="n">
+        <v>101</v>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1537" t="n">
+        <v>46290.04166666666</v>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="n">
+        <v>1537</v>
+      </c>
+      <c r="B1538" t="n">
+        <v>102</v>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1538" t="n">
+        <v>46276.04166666666</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="n">
+        <v>1538</v>
+      </c>
+      <c r="B1539" t="n">
+        <v>103</v>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1539" t="n">
+        <v>46282.29166666666</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="n">
+        <v>1539</v>
+      </c>
+      <c r="B1540" t="n">
+        <v>104</v>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1540" t="n">
+        <v>46290.08333333334</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="n">
+        <v>1540</v>
+      </c>
+      <c r="B1541" t="n">
+        <v>105</v>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1541" t="n">
+        <v>46278.125</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="n">
+        <v>1541</v>
+      </c>
+      <c r="B1542" t="n">
+        <v>106</v>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1542" t="n">
+        <v>46275.29166666666</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="n">
+        <v>1542</v>
+      </c>
+      <c r="B1543" t="n">
+        <v>107</v>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1543" t="n">
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="n">
+        <v>1543</v>
+      </c>
+      <c r="B1544" t="n">
+        <v>108</v>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1544" t="n">
+        <v>46283.08333333334</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="n">
+        <v>1544</v>
+      </c>
+      <c r="B1545" t="n">
+        <v>109</v>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1545" t="n">
+        <v>46285.20833333334</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="n">
+        <v>1545</v>
+      </c>
+      <c r="B1546" t="n">
+        <v>110</v>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1546" t="n">
+        <v>46289.04166666666</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="n">
+        <v>1546</v>
+      </c>
+      <c r="B1547" t="n">
+        <v>111</v>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1547" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="n">
+        <v>1547</v>
+      </c>
+      <c r="B1548" t="n">
+        <v>112</v>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1548" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="n">
+        <v>1548</v>
+      </c>
+      <c r="B1549" t="n">
+        <v>113</v>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1549" t="n">
+        <v>46280.25</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="n">
+        <v>1549</v>
+      </c>
+      <c r="B1550" t="n">
+        <v>114</v>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1550" t="n">
+        <v>46283.20833333334</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="n">
+        <v>1550</v>
+      </c>
+      <c r="B1551" t="n">
+        <v>115</v>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1551" t="n">
+        <v>46294.33333333334</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="n">
+        <v>1551</v>
+      </c>
+      <c r="B1552" t="n">
+        <v>116</v>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1552" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="n">
+        <v>1552</v>
+      </c>
+      <c r="B1553" t="n">
+        <v>117</v>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1553" t="n">
+        <v>46283.33333333334</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="n">
+        <v>1553</v>
+      </c>
+      <c r="B1554" t="n">
+        <v>118</v>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1554" t="n">
+        <v>46280.375</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="n">
+        <v>1554</v>
+      </c>
+      <c r="B1555" t="n">
+        <v>119</v>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1555" t="n">
+        <v>46290.33333333334</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="n">
+        <v>1555</v>
+      </c>
+      <c r="B1556" t="n">
+        <v>120</v>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1556" t="n">
+        <v>46276.375</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="n">
+        <v>1556</v>
+      </c>
+      <c r="B1557" t="n">
+        <v>121</v>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1557" t="n">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B1558" t="n">
+        <v>122</v>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1558" t="n">
+        <v>46268.20833333334</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B1559" t="n">
+        <v>123</v>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1559" t="n">
+        <v>46276.25</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="n">
+        <v>1559</v>
+      </c>
+      <c r="B1560" t="n">
+        <v>124</v>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1560" t="n">
+        <v>46291.20833333334</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="n">
+        <v>1560</v>
+      </c>
+      <c r="B1561" t="n">
+        <v>125</v>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1561" t="n">
+        <v>46271.20833333334</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="n">
+        <v>1561</v>
+      </c>
+      <c r="B1562" t="n">
+        <v>126</v>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1562" t="n">
+        <v>46279.16666666666</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="n">
+        <v>1562</v>
+      </c>
+      <c r="B1563" t="n">
+        <v>127</v>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1563" t="n">
+        <v>46271.25</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="n">
+        <v>1563</v>
+      </c>
+      <c r="B1564" t="n">
+        <v>128</v>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1564" t="n">
+        <v>46280.41666666666</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="n">
+        <v>1564</v>
+      </c>
+      <c r="B1565" t="n">
+        <v>129</v>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1565" t="n">
+        <v>46290.08333333334</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="n">
+        <v>1565</v>
+      </c>
+      <c r="B1566" t="n">
+        <v>130</v>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1566" t="n">
+        <v>46284.25</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="n">
+        <v>1566</v>
+      </c>
+      <c r="B1567" t="n">
+        <v>131</v>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1567" t="n">
+        <v>46290.16666666666</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="n">
+        <v>1567</v>
+      </c>
+      <c r="B1568" t="n">
+        <v>132</v>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1568" t="n">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="n">
+        <v>1568</v>
+      </c>
+      <c r="B1569" t="n">
+        <v>133</v>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1569" t="n">
+        <v>46290.04166666666</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="n">
+        <v>1569</v>
+      </c>
+      <c r="B1570" t="n">
+        <v>134</v>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1570" t="n">
+        <v>46282.25</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="n">
+        <v>1570</v>
+      </c>
+      <c r="B1571" t="n">
+        <v>135</v>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1571" t="n">
+        <v>46280.33333333334</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="n">
+        <v>1571</v>
+      </c>
+      <c r="B1572" t="n">
+        <v>136</v>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1572" t="n">
+        <v>46279.375</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="n">
+        <v>1572</v>
+      </c>
+      <c r="B1573" t="n">
+        <v>137</v>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1573" t="n">
+        <v>46289.33333333334</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="n">
+        <v>1573</v>
+      </c>
+      <c r="B1574" t="n">
+        <v>138</v>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1574" t="n">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="n">
+        <v>1574</v>
+      </c>
+      <c r="B1575" t="n">
+        <v>139</v>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1575" t="n">
+        <v>46272.08333333334</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="n">
+        <v>1575</v>
+      </c>
+      <c r="B1576" t="n">
+        <v>140</v>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1576" t="n">
+        <v>46287.04166666666</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="n">
+        <v>1576</v>
+      </c>
+      <c r="B1577" t="n">
+        <v>141</v>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1577" t="n">
+        <v>46273.41666666666</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="n">
+        <v>1577</v>
+      </c>
+      <c r="B1578" t="n">
+        <v>142</v>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1578" t="n">
+        <v>46286.29166666666</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="n">
+        <v>1578</v>
+      </c>
+      <c r="B1579" t="n">
+        <v>143</v>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1579" t="n">
+        <v>46292.125</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="n">
+        <v>1579</v>
+      </c>
+      <c r="B1580" t="n">
+        <v>144</v>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1580" t="n">
+        <v>46273.08333333334</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="n">
+        <v>1580</v>
+      </c>
+      <c r="B1581" t="n">
+        <v>145</v>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1581" t="n">
+        <v>46281.04166666666</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="n">
+        <v>1581</v>
+      </c>
+      <c r="B1582" t="n">
+        <v>146</v>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1582" t="n">
+        <v>46284.125</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="n">
+        <v>1582</v>
+      </c>
+      <c r="B1583" t="n">
+        <v>147</v>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1583" t="n">
+        <v>46281.04166666666</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="n">
+        <v>1583</v>
+      </c>
+      <c r="B1584" t="n">
+        <v>148</v>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1584" t="n">
+        <v>46278.25</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="n">
+        <v>1584</v>
+      </c>
+      <c r="B1585" t="n">
+        <v>149</v>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1585" t="n">
+        <v>46288.29166666666</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="n">
+        <v>1585</v>
+      </c>
+      <c r="B1586" t="n">
+        <v>150</v>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1586" t="n">
+        <v>46272.29166666666</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="n">
+        <v>1586</v>
+      </c>
+      <c r="B1587" t="n">
+        <v>151</v>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1587" t="n">
+        <v>46292.25</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="n">
+        <v>1587</v>
+      </c>
+      <c r="B1588" t="n">
+        <v>152</v>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1588" t="n">
+        <v>46290.375</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="n">
+        <v>1588</v>
+      </c>
+      <c r="B1589" t="n">
+        <v>153</v>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1589" t="n">
+        <v>46277.16666666666</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="n">
+        <v>1589</v>
+      </c>
+      <c r="B1590" t="n">
+        <v>154</v>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1590" t="n">
+        <v>46272.25</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="n">
+        <v>1590</v>
+      </c>
+      <c r="B1591" t="n">
+        <v>155</v>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1591" t="n">
+        <v>46290.41666666666</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="n">
+        <v>1591</v>
+      </c>
+      <c r="B1592" t="n">
+        <v>156</v>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1592" t="n">
+        <v>46289.33333333334</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="n">
+        <v>1592</v>
+      </c>
+      <c r="B1593" t="n">
+        <v>157</v>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1593" t="n">
+        <v>46267.29166666666</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="n">
+        <v>1593</v>
+      </c>
+      <c r="B1594" t="n">
+        <v>158</v>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1594" t="n">
+        <v>46293.20833333334</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="n">
+        <v>1594</v>
+      </c>
+      <c r="B1595" t="n">
+        <v>159</v>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1595" t="n">
+        <v>46274.29166666666</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="n">
+        <v>1595</v>
+      </c>
+      <c r="B1596" t="n">
+        <v>160</v>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1596" t="n">
+        <v>46292.41666666666</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="n">
+        <v>1596</v>
+      </c>
+      <c r="B1597" t="n">
+        <v>161</v>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1597" t="n">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="n">
+        <v>1597</v>
+      </c>
+      <c r="B1598" t="n">
+        <v>162</v>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1598" t="n">
+        <v>46285.08333333334</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="n">
+        <v>1598</v>
+      </c>
+      <c r="B1599" t="n">
+        <v>163</v>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1599" t="n">
+        <v>46281.25</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="n">
+        <v>1599</v>
+      </c>
+      <c r="B1600" t="n">
+        <v>164</v>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1600" t="n">
+        <v>46285.375</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="n">
+        <v>1600</v>
+      </c>
+      <c r="B1601" t="n">
+        <v>165</v>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1601" t="n">
+        <v>46285.16666666666</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="n">
+        <v>1601</v>
+      </c>
+      <c r="B1602" t="n">
+        <v>166</v>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1602" t="n">
+        <v>46283.125</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="n">
+        <v>1602</v>
+      </c>
+      <c r="B1603" t="n">
+        <v>167</v>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1603" t="n">
+        <v>46286.375</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="n">
+        <v>1603</v>
+      </c>
+      <c r="B1604" t="n">
+        <v>168</v>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1604" t="n">
+        <v>46279.29166666666</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="n">
+        <v>1604</v>
+      </c>
+      <c r="B1605" t="n">
+        <v>169</v>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1605" t="n">
+        <v>46283.33333333334</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="n">
+        <v>1605</v>
+      </c>
+      <c r="B1606" t="n">
+        <v>170</v>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1606" t="n">
+        <v>46271.33333333334</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="n">
+        <v>1606</v>
+      </c>
+      <c r="B1607" t="n">
+        <v>171</v>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1607" t="n">
+        <v>46288.33333333334</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="n">
+        <v>1607</v>
+      </c>
+      <c r="B1608" t="n">
+        <v>172</v>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1608" t="n">
+        <v>46292.29166666666</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="n">
+        <v>1608</v>
+      </c>
+      <c r="B1609" t="n">
+        <v>173</v>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1609" t="n">
+        <v>46275.20833333334</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="n">
+        <v>1609</v>
+      </c>
+      <c r="B1610" t="n">
+        <v>174</v>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1610" t="n">
+        <v>46283.41666666666</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="n">
+        <v>1610</v>
+      </c>
+      <c r="B1611" t="n">
+        <v>175</v>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1611" t="n">
+        <v>46286.20833333334</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="n">
+        <v>1611</v>
+      </c>
+      <c r="B1612" t="n">
+        <v>176</v>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1612" t="n">
+        <v>46283.375</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="n">
+        <v>1612</v>
+      </c>
+      <c r="B1613" t="n">
+        <v>177</v>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1613" t="n">
+        <v>46279.125</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="n">
+        <v>1613</v>
+      </c>
+      <c r="B1614" t="n">
+        <v>178</v>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1614" t="n">
+        <v>46292.375</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="n">
+        <v>1614</v>
+      </c>
+      <c r="B1615" t="n">
+        <v>179</v>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1615" t="n">
+        <v>46289.04166666666</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="n">
+        <v>1615</v>
+      </c>
+      <c r="B1616" t="n">
+        <v>180</v>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1616" t="n">
+        <v>46269.16666666666</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="n">
+        <v>1616</v>
+      </c>
+      <c r="B1617" t="n">
+        <v>181</v>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1617" t="n">
+        <v>46280.25</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="n">
+        <v>1617</v>
+      </c>
+      <c r="B1618" t="n">
+        <v>182</v>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1618" t="n">
+        <v>46269.33333333334</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="n">
+        <v>1618</v>
+      </c>
+      <c r="B1619" t="n">
+        <v>183</v>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1619" t="n">
+        <v>46285.375</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="n">
+        <v>1619</v>
+      </c>
+      <c r="B1620" t="n">
+        <v>184</v>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1620" t="n">
+        <v>46291.125</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="n">
+        <v>1620</v>
+      </c>
+      <c r="B1621" t="n">
+        <v>185</v>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1621" t="n">
+        <v>46271.04166666666</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="n">
+        <v>1621</v>
+      </c>
+      <c r="B1622" t="n">
+        <v>186</v>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1622" t="n">
+        <v>46285.375</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="n">
+        <v>1622</v>
+      </c>
+      <c r="B1623" t="n">
+        <v>187</v>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1623" t="n">
+        <v>46293.33333333334</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="n">
+        <v>1623</v>
+      </c>
+      <c r="B1624" t="n">
+        <v>188</v>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1624" t="n">
+        <v>46278.08333333334</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="n">
+        <v>1624</v>
+      </c>
+      <c r="B1625" t="n">
+        <v>189</v>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1625" t="n">
+        <v>46289.16666666666</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="n">
+        <v>1625</v>
+      </c>
+      <c r="B1626" t="n">
+        <v>190</v>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1626" t="n">
+        <v>46283.16666666666</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="n">
+        <v>1626</v>
+      </c>
+      <c r="B1627" t="n">
+        <v>191</v>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1627" t="n">
+        <v>46271.125</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="n">
+        <v>1627</v>
+      </c>
+      <c r="B1628" t="n">
+        <v>192</v>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1628" t="n">
+        <v>46280.125</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="n">
+        <v>1628</v>
+      </c>
+      <c r="B1629" t="n">
+        <v>193</v>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1629" t="n">
+        <v>46282.16666666666</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="n">
+        <v>1629</v>
+      </c>
+      <c r="B1630" t="n">
+        <v>194</v>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1630" t="n">
+        <v>46275.16666666666</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="n">
+        <v>1630</v>
+      </c>
+      <c r="B1631" t="n">
+        <v>195</v>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1631" t="n">
+        <v>46269.04166666666</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="n">
+        <v>1631</v>
+      </c>
+      <c r="B1632" t="n">
+        <v>196</v>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1632" t="n">
+        <v>46271.25</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="n">
+        <v>1632</v>
+      </c>
+      <c r="B1633" t="n">
+        <v>197</v>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1633" t="n">
+        <v>46274.20833333334</v>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="n">
+        <v>1633</v>
+      </c>
+      <c r="B1634" t="n">
+        <v>198</v>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1634" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="n">
+        <v>1634</v>
+      </c>
+      <c r="B1635" t="n">
+        <v>199</v>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1635" t="n">
+        <v>46275.375</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="n">
+        <v>1635</v>
+      </c>
+      <c r="B1636" t="n">
+        <v>200</v>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1636" t="n">
+        <v>46288.33333333334</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="n">
+        <v>1636</v>
+      </c>
+      <c r="B1637" t="n">
+        <v>201</v>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1637" t="n">
+        <v>46278.33333333334</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="n">
+        <v>1637</v>
+      </c>
+      <c r="B1638" t="n">
+        <v>202</v>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1638" t="n">
+        <v>46287.04166666666</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="n">
+        <v>1638</v>
+      </c>
+      <c r="B1639" t="n">
+        <v>203</v>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1639" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="n">
+        <v>1639</v>
+      </c>
+      <c r="B1640" t="n">
+        <v>204</v>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1640" t="n">
+        <v>46291.125</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="n">
+        <v>1640</v>
+      </c>
+      <c r="B1641" t="n">
+        <v>205</v>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1641" t="n">
+        <v>46280.125</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="n">
+        <v>1641</v>
+      </c>
+      <c r="B1642" t="n">
+        <v>206</v>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1642" t="n">
+        <v>46288.125</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="n">
+        <v>1642</v>
+      </c>
+      <c r="B1643" t="n">
+        <v>207</v>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1643" t="n">
+        <v>46269.25</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="n">
+        <v>1643</v>
+      </c>
+      <c r="B1644" t="n">
+        <v>208</v>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1644" t="n">
+        <v>46276.20833333334</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="n">
+        <v>1644</v>
+      </c>
+      <c r="B1645" t="n">
+        <v>209</v>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1645" t="n">
+        <v>46269.41666666666</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="n">
+        <v>1645</v>
+      </c>
+      <c r="B1646" t="n">
+        <v>210</v>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1646" t="n">
+        <v>46286.41666666666</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="n">
+        <v>1646</v>
+      </c>
+      <c r="B1647" t="n">
+        <v>211</v>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1647" t="n">
+        <v>46283.16666666666</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="n">
+        <v>1647</v>
+      </c>
+      <c r="B1648" t="n">
+        <v>212</v>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1648" t="n">
+        <v>46274.20833333334</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="n">
+        <v>1648</v>
+      </c>
+      <c r="B1649" t="n">
+        <v>213</v>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1649" t="n">
+        <v>46283.29166666666</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="n">
+        <v>1649</v>
+      </c>
+      <c r="B1650" t="n">
+        <v>214</v>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1650" t="n">
+        <v>46273.375</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="n">
+        <v>1650</v>
+      </c>
+      <c r="B1651" t="n">
+        <v>215</v>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1651" t="n">
+        <v>46290.08333333334</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="n">
+        <v>1651</v>
+      </c>
+      <c r="B1652" t="n">
+        <v>216</v>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1652" t="n">
+        <v>46283.16666666666</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="n">
+        <v>1652</v>
+      </c>
+      <c r="B1653" t="n">
+        <v>217</v>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1653" t="n">
+        <v>46272.41666666666</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="n">
+        <v>1653</v>
+      </c>
+      <c r="B1654" t="n">
+        <v>218</v>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1654" t="n">
+        <v>46283.16666666666</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="n">
+        <v>1654</v>
+      </c>
+      <c r="B1655" t="n">
+        <v>219</v>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1655" t="n">
+        <v>46285.04166666666</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="n">
+        <v>1655</v>
+      </c>
+      <c r="B1656" t="n">
+        <v>220</v>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1656" t="n">
+        <v>46275.125</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="n">
+        <v>1656</v>
+      </c>
+      <c r="B1657" t="n">
+        <v>221</v>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1657" t="n">
+        <v>46283.41666666666</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="n">
+        <v>1657</v>
+      </c>
+      <c r="B1658" t="n">
+        <v>222</v>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1658" t="n">
+        <v>46279.41666666666</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="n">
+        <v>1658</v>
+      </c>
+      <c r="B1659" t="n">
+        <v>223</v>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1659" t="n">
+        <v>46269.375</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="n">
+        <v>1659</v>
+      </c>
+      <c r="B1660" t="n">
+        <v>224</v>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1660" t="n">
+        <v>46272.08333333334</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="n">
+        <v>1660</v>
+      </c>
+      <c r="B1661" t="n">
+        <v>225</v>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1661" t="n">
+        <v>46279.04166666666</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="n">
+        <v>1661</v>
+      </c>
+      <c r="B1662" t="n">
+        <v>226</v>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1662" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="n">
+        <v>1662</v>
+      </c>
+      <c r="B1663" t="n">
+        <v>227</v>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1663" t="n">
+        <v>46291.29166666666</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="n">
+        <v>1663</v>
+      </c>
+      <c r="B1664" t="n">
+        <v>228</v>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1664" t="n">
+        <v>46287.125</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="n">
+        <v>1664</v>
+      </c>
+      <c r="B1665" t="n">
+        <v>229</v>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1665" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="n">
+        <v>1665</v>
+      </c>
+      <c r="B1666" t="n">
+        <v>230</v>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1666" t="n">
+        <v>46278.29166666666</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="n">
+        <v>1666</v>
+      </c>
+      <c r="B1667" t="n">
+        <v>231</v>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1667" t="n">
+        <v>46283.04166666666</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="n">
+        <v>1667</v>
+      </c>
+      <c r="B1668" t="n">
+        <v>232</v>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1668" t="n">
+        <v>46291.125</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="n">
+        <v>1668</v>
+      </c>
+      <c r="B1669" t="n">
+        <v>233</v>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1669" t="n">
+        <v>46271.16666666666</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="n">
+        <v>1669</v>
+      </c>
+      <c r="B1670" t="n">
+        <v>234</v>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1670" t="n">
+        <v>46277.20833333334</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="n">
+        <v>1670</v>
+      </c>
+      <c r="B1671" t="n">
+        <v>235</v>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1671" t="n">
+        <v>46285.125</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="n">
+        <v>1671</v>
+      </c>
+      <c r="B1672" t="n">
+        <v>236</v>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1672" t="n">
+        <v>46270.33333333334</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="n">
+        <v>1672</v>
+      </c>
+      <c r="B1673" t="n">
+        <v>237</v>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1673" t="n">
+        <v>46291.16666666666</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="n">
+        <v>1673</v>
+      </c>
+      <c r="B1674" t="n">
+        <v>238</v>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1674" t="n">
+        <v>46276.20833333334</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="n">
+        <v>1674</v>
+      </c>
+      <c r="B1675" t="n">
+        <v>239</v>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1675" t="n">
+        <v>46289.08333333334</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="n">
+        <v>1675</v>
+      </c>
+      <c r="B1676" t="n">
+        <v>240</v>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1676" t="n">
+        <v>46270.20833333334</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="n">
+        <v>1676</v>
+      </c>
+      <c r="B1677" t="n">
+        <v>241</v>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1677" t="n">
+        <v>46274.41666666666</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="n">
+        <v>1677</v>
+      </c>
+      <c r="B1678" t="n">
+        <v>242</v>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1678" t="n">
+        <v>46274.125</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="n">
+        <v>1678</v>
+      </c>
+      <c r="B1679" t="n">
+        <v>243</v>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1679" t="n">
+        <v>46268.16666666666</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="n">
+        <v>1679</v>
+      </c>
+      <c r="B1680" t="n">
+        <v>244</v>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1680" t="n">
+        <v>46278.04166666666</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="n">
+        <v>1680</v>
+      </c>
+      <c r="B1681" t="n">
+        <v>245</v>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1681" t="n">
+        <v>46279.375</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="n">
+        <v>1681</v>
+      </c>
+      <c r="B1682" t="n">
+        <v>246</v>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1682" t="n">
+        <v>46277.16666666666</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="n">
+        <v>1682</v>
+      </c>
+      <c r="B1683" t="n">
+        <v>247</v>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1683" t="n">
+        <v>46266.25</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="n">
+        <v>1683</v>
+      </c>
+      <c r="B1684" t="n">
+        <v>248</v>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1684" t="n">
+        <v>46274.375</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="n">
+        <v>1684</v>
+      </c>
+      <c r="B1685" t="n">
+        <v>249</v>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1685" t="n">
+        <v>46269.33333333334</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="n">
+        <v>1685</v>
+      </c>
+      <c r="B1686" t="n">
+        <v>250</v>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1686" t="n">
+        <v>46292.41666666666</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="n">
+        <v>1686</v>
+      </c>
+      <c r="B1687" t="n">
+        <v>251</v>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1687" t="n">
+        <v>46267.41666666666</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="n">
+        <v>1687</v>
+      </c>
+      <c r="B1688" t="n">
+        <v>252</v>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1688" t="n">
+        <v>46270.33333333334</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="n">
+        <v>1688</v>
+      </c>
+      <c r="B1689" t="n">
+        <v>253</v>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1689" t="n">
+        <v>46273.33333333334</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="n">
+        <v>1689</v>
+      </c>
+      <c r="B1690" t="n">
+        <v>254</v>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1690" t="n">
+        <v>46286.375</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="n">
+        <v>1690</v>
+      </c>
+      <c r="B1691" t="n">
+        <v>255</v>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1691" t="n">
+        <v>46288.41666666666</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="n">
+        <v>1691</v>
+      </c>
+      <c r="B1692" t="n">
+        <v>256</v>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1692" t="n">
+        <v>46279.08333333334</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="n">
+        <v>1692</v>
+      </c>
+      <c r="B1693" t="n">
+        <v>257</v>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1693" t="n">
+        <v>46293.29166666666</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="n">
+        <v>1693</v>
+      </c>
+      <c r="B1694" t="n">
+        <v>258</v>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1694" t="n">
+        <v>46293.04166666666</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="n">
+        <v>1694</v>
+      </c>
+      <c r="B1695" t="n">
+        <v>259</v>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1695" t="n">
+        <v>46276.125</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="n">
+        <v>1695</v>
+      </c>
+      <c r="B1696" t="n">
+        <v>260</v>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1696" t="n">
+        <v>46290.41666666666</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="n">
+        <v>1696</v>
+      </c>
+      <c r="B1697" t="n">
+        <v>261</v>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1697" t="n">
+        <v>46282.41666666666</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="n">
+        <v>1697</v>
+      </c>
+      <c r="B1698" t="n">
+        <v>262</v>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1698" t="n">
+        <v>46282.125</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="n">
+        <v>1698</v>
+      </c>
+      <c r="B1699" t="n">
+        <v>263</v>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1699" t="n">
+        <v>46292.125</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="n">
+        <v>1699</v>
+      </c>
+      <c r="B1700" t="n">
+        <v>264</v>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1700" t="n">
+        <v>46269.20833333334</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="n">
+        <v>1700</v>
+      </c>
+      <c r="B1701" t="n">
+        <v>265</v>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1701" t="n">
+        <v>46271.29166666666</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B1702" t="n">
+        <v>266</v>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1702" t="n">
+        <v>46285.16666666666</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="n">
+        <v>1702</v>
+      </c>
+      <c r="B1703" t="n">
+        <v>267</v>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1703" t="n">
+        <v>46291.25</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B1704" t="n">
+        <v>268</v>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1704" t="n">
+        <v>46279.375</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B1705" t="n">
+        <v>269</v>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1705" t="n">
+        <v>46292.25</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B1706" t="n">
+        <v>270</v>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1706" t="n">
+        <v>46277.41666666666</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B1707" t="n">
+        <v>271</v>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1707" t="n">
+        <v>46289.04166666666</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="n">
+        <v>1707</v>
+      </c>
+      <c r="B1708" t="n">
+        <v>272</v>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1708" t="n">
+        <v>46278.08333333334</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="n">
+        <v>1708</v>
+      </c>
+      <c r="B1709" t="n">
+        <v>273</v>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1709" t="n">
+        <v>46267.04166666666</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B1710" t="n">
+        <v>274</v>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1710" t="n">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="n">
+        <v>1710</v>
+      </c>
+      <c r="B1711" t="n">
+        <v>275</v>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1711" t="n">
+        <v>46291.33333333334</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="n">
+        <v>1711</v>
+      </c>
+      <c r="B1712" t="n">
+        <v>276</v>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1712" t="n">
+        <v>46268.125</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="n">
+        <v>1712</v>
+      </c>
+      <c r="B1713" t="n">
+        <v>277</v>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1713" t="n">
+        <v>46266.41666666666</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="n">
+        <v>1713</v>
+      </c>
+      <c r="B1714" t="n">
+        <v>278</v>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>NEGATIVE</t>
+        </is>
+      </c>
+      <c r="E1714" t="n">
+        <v>46282.20833333334</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="n">
+        <v>1714</v>
+      </c>
+      <c r="B1715" t="n">
+        <v>279</v>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1715" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="n">
+        <v>1715</v>
+      </c>
+      <c r="B1716" t="n">
+        <v>280</v>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1716" t="n">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="n">
+        <v>1716</v>
+      </c>
+      <c r="B1717" t="n">
+        <v>281</v>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1717" t="n">
+        <v>46287.08333333334</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="n">
+        <v>1717</v>
+      </c>
+      <c r="B1718" t="n">
+        <v>282</v>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1718" t="n">
+        <v>46279.41666666666</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="n">
+        <v>1718</v>
+      </c>
+      <c r="B1719" t="n">
+        <v>283</v>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1719" t="n">
+        <v>46268.08333333334</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="n">
+        <v>1719</v>
+      </c>
+      <c r="B1720" t="n">
+        <v>284</v>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1720" t="n">
+        <v>46269.41666666666</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="n">
+        <v>1720</v>
+      </c>
+      <c r="B1721" t="n">
+        <v>285</v>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1721" t="n">
+        <v>46278.20833333334</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="n">
+        <v>1721</v>
+      </c>
+      <c r="B1722" t="n">
+        <v>286</v>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>POSITIVE</t>
+        </is>
+      </c>
+      <c r="E1722" t="n">
+        <v>46278.29166666666</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="n">
+        <v>1722</v>
+      </c>
+      <c r="B1723" t="n">
+        <v>287</v>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>WEIGHT_VITALITY</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="E1723" t="n">
         <v>46274.125</v>
       </c>
     </row>
